--- a/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1430,7 +1430,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">ahead.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参ったね。…でも忘れないよ</t>
+          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">behind.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1487,14 +1487,14 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅ。やっと終わったか</t>
+          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…ま、笑えるよ。最高の相手だった</t>
+          <t xml:space="preserve">…参ったね。…でも忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
@@ -1551,14 +1551,14 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相手だったよ。…これからもよろしく</t>
+          <t xml:space="preserve">…ふぅ。やっと終わったか</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">loser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1583,14 +1583,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いよいよだね。…全部出し切るよ</t>
+          <t xml:space="preserve">負けたけど…ま、笑えるよ。最高の相手だった</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">winner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1615,14 +1615,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっけー。全力でいくよ</t>
+          <t xml:space="preserve">最高の相手だったよ。…これからもよろしく</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
@@ -1647,14 +1647,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…全部出し切る。今日で</t>
+          <t xml:space="preserve">いよいよだね。…全部出し切るよ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
@@ -1679,14 +1679,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。言葉はいらない</t>
+          <t xml:space="preserve">おっけー。全力でいくよ</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さて、そろそろ片付けようか</t>
+          <t xml:space="preserve">…全部出し切る。今日で</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
@@ -1743,14 +1743,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいよ、来なよ。相手してあげる</t>
+          <t xml:space="preserve">…うん。言葉はいらない</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">attacker.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最後か。全部出し切ろう</t>
+          <t xml:space="preserve">さて、そろそろ片付けようか</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing.composed[1]</t>
+          <t xml:space="preserve">defender.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1807,14 +1807,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。最高の締めにしよう</t>
+          <t xml:space="preserve">いいよ、来なよ。相手してあげる</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">…最後か。全部出し切ろう</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateDefender.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つ勝ち。…でもまだまだだね</t>
+          <t xml:space="preserve">…うん。最高の締めにしよう</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.easygoing.composed[1]</t>
+          <t xml:space="preserve">loserLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">winnerLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと一つ勝てた。…でも、まだ終わってないね</t>
+          <t xml:space="preserve">一つ勝ち。…でもまだまだだね</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateLoser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateWinner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったか。…でもまだ、終わった気はしないね</t>
+          <t xml:space="preserve">やっと一つ勝てた。…でも、まだ終わってないね</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">loser.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2031,14 +2031,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…嘘だろう。…こんなことが</t>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">winner.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2063,14 +2063,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝っちゃった。…ふぅん</t>
+          <t xml:space="preserve">勝ったか。…でもまだ、終わった気はしないね</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.easygoing.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.easygoing.composed[1]</t>
+          <t xml:space="preserve">loserLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2095,14 +2095,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}の笑顔が消えた。「…さすがにね。…こっちも本気で行くよ」</t>
+          <t xml:space="preserve">…嘘だろう。…こんなことが</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2112,29 +2112,29 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.lose[1]</t>
+          <t xml:space="preserve">winnerLines.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃった。……ごめんね、社長。</t>
+          <t xml:space="preserve">…勝っちゃった。…ふぅん</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2144,29 +2144,29 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.lose[2]</t>
+          <t xml:space="preserve">awakening.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……だめだったよ。悔しいなって、ちゃんと思ってる。</t>
+          <t xml:space="preserve">{nameB}の笑顔が消えた。「…さすがにね。…こっちも本気で行くよ」</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.lose[3]</t>
+          <t xml:space="preserve">composed_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2191,14 +2191,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てなかった。……次はもう少し、うまくやるよ。</t>
+          <t xml:space="preserve">負けちゃった。……ごめんね、社長。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.petition[1]</t>
+          <t xml:space="preserve">composed_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2223,14 +2223,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといい? ……やってみたい相手がいるの。</t>
+          <t xml:space="preserve">……だめだったよ。悔しいなって、ちゃんと思ってる。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.petition[2]</t>
+          <t xml:space="preserve">composed_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あのね。あの人と、やらせてもらえないかな。</t>
+          <t xml:space="preserve">勝てなかった。……次はもう少し、うまくやるよ。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.petition[1]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.petition[3]</t>
+          <t xml:space="preserve">composed_easygoing.petition[1]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるんだけど。……あの相手、私に回してくれない?</t>
+          <t xml:space="preserve">社長、ちょっといい? ……やってみたい相手がいるの。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.petition[2]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.sendoff[1]</t>
+          <t xml:space="preserve">composed_easygoing.petition[2]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2319,14 +2319,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとね、社長。……行ってくる。</t>
+          <t xml:space="preserve">……あのね。あの人と、やらせてもらえないかな。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.petition[3]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.sendoff[2]</t>
+          <t xml:space="preserve">composed_easygoing.petition[3]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、通しちゃうんだ。……うん、ありがと。</t>
+          <t xml:space="preserve">お願いがあるんだけど。……あの相手、私に回してくれない?</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.sendoff[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.sendoff[3]</t>
+          <t xml:space="preserve">composed_easygoing.sendoff[1]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2383,14 +2383,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">助かるよ。……のんびりしてる場合じゃないね。</t>
+          <t xml:space="preserve">ありがとね、社長。……行ってくる。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.sendoff[2]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.win[1]</t>
+          <t xml:space="preserve">composed_easygoing.sendoff[2]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2415,14 +2415,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。……わがまま聞いてくれて、ありがとね。</t>
+          <t xml:space="preserve">ふふ、通しちゃうんだ。……うん、ありがと。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.sendoff[3]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.win[2]</t>
+          <t xml:space="preserve">composed_easygoing.sendoff[3]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2447,14 +2447,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ほら、心配なかったでしょ。ちゃんと勝ったよ。</t>
+          <t xml:space="preserve">助かるよ。……のんびりしてる場合じゃないね。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.win[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.win[3]</t>
+          <t xml:space="preserve">composed_easygoing.win[1]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2479,14 +2479,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったよ。……うん、いい気分。</t>
+          <t xml:space="preserve">勝っちゃった。……わがまま聞いてくれて、ありがとね。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.win[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing._accept[1]</t>
+          <t xml:space="preserve">composed_easygoing.win[2]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたし? ま、いいよ。付き合う。</t>
+          <t xml:space="preserve">……ほら、心配なかったでしょ。ちゃんと勝ったよ。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_easygoing.win[3]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing._accept[2]</t>
+          <t xml:space="preserve">composed_easygoing.win[3]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ、名指しか。…断る理由もないかな。</t>
+          <t xml:space="preserve">勝ったよ。……うん、いい気分。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing._accept[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing._accept[3]</t>
+          <t xml:space="preserve">composed_easygoing._accept[1]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2575,14 +2575,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そんなに気合い入れなくていいよ。…受けるから。</t>
+          <t xml:space="preserve">…あたし? ま、いいよ。付き合う。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing._accept[2]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.draw[1]</t>
+          <t xml:space="preserve">composed_easygoing._accept[2]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…引き分けか。まあ、そういう日もある。</t>
+          <t xml:space="preserve">へえ、名指しか。…断る理由もないかな。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing._accept[3]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.draw[2]</t>
+          <t xml:space="preserve">composed_easygoing._accept[3]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決まらなかったね。…また今度でいいよ。</t>
+          <t xml:space="preserve">そんなに気合い入れなくていいよ。…受けるから。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.draw[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.draw[3]</t>
+          <t xml:space="preserve">composed_easygoing.draw[1]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2671,14 +2671,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お互い、まだ余ってるね。…楽しみだ。</t>
+          <t xml:space="preserve">…決着つかずか。まあ、そういう日もある。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.draw[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.lose[1]</t>
+          <t xml:space="preserve">composed_easygoing.draw[2]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2703,14 +2703,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あー…やられた。まいったな。</t>
+          <t xml:space="preserve">決まらなかったね。…また今度でいいよ。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.draw[3]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.lose[2]</t>
+          <t xml:space="preserve">composed_easygoing.draw[3]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うん、あんたの勝ち。…強かったよ。</t>
+          <t xml:space="preserve">お互い、まだ余ってるね。…楽しみだ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.lose[3]</t>
+          <t xml:space="preserve">composed_easygoing.lose[1]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…完敗。言い訳はしないよ。</t>
+          <t xml:space="preserve">あー…やられた。まいったな。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.win[1]</t>
+          <t xml:space="preserve">composed_easygoing.lose[2]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんかな。悪くなかったよ。</t>
+          <t xml:space="preserve">うん、あんたの勝ち。…強かったよ。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.win[2]</t>
+          <t xml:space="preserve">composed_easygoing.lose[3]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2831,14 +2831,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんた、力入りすぎ。…だから届かない。</t>
+          <t xml:space="preserve">…完敗。言い訳はしないよ。</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.win[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_easygoing.win[3]</t>
+          <t xml:space="preserve">composed_easygoing.win[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2863,14 +2863,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃったね。…気にしなくていいよ。</t>
+          <t xml:space="preserve">…ま、こんなもんかな。悪くなかったよ。</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.win[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2880,29 +2880,29 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed_easygoing.win[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、もうちょっとやってみるか</t>
+          <t xml:space="preserve">あんた、力入りすぎ。…だから届かない。</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_easygoing.win[3]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2912,29 +2912,29 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed_easygoing.win[3]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もうちょっとだけ。…あのベルト、もう一回触りたいんだ</t>
+          <t xml:space="preserve">勝っちゃったね。…気にしなくていいよ。</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">accepted.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2959,14 +2959,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ使ってくれるんだ。…ま、いいよ</t>
+          <t xml:space="preserve">…お世話になったね。…また、どこかで会えたらいいな</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.easygoing.composed[1]</t>
+          <t xml:space="preserve">accepted.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ必要としてくれるんだ。…じゃあもう少し</t>
+          <t xml:space="preserve">…じゃ、行ってくるよ</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">defended.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト持てたしね。…十分だよ</t>
+          <t xml:space="preserve">…引き留めてくれるんだ。…嬉しいね</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">defended.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3055,14 +3055,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、潮時だね。…わかったよ</t>
+          <t xml:space="preserve">…残るよ。これからもよろしく</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.easygoing.composed[1]</t>
+          <t xml:space="preserve">defense_failed.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…覚悟はできてた。…最後、よろしくね</t>
+          <t xml:space="preserve">…ごめんね。引き留めてもらったのに…</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.composed[1]</t>
+          <t xml:space="preserve">defense_failed.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3119,14 +3119,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、そうだよね。…ありがとう</t>
+          <t xml:space="preserve">…元気でね</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.easygoing.composed[1]</t>
+          <t xml:space="preserve">default.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3151,14 +3151,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、勝てなくなったもんね。…仕方ないか</t>
+          <t xml:space="preserve">…まあ、もうちょっとやってみるか</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">former_champ.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3183,14 +3183,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだチャンピオンだよ。…もう少し待って</t>
+          <t xml:space="preserve">…もうちょっとだけ。…あのベルト、もう一回触りたいんだ</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.easygoing.composed[1]</t>
+          <t xml:space="preserve">heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…邪魔なの、か。…まあ、ちょっとひどいね</t>
+          <t xml:space="preserve">…まだ使ってくれるんだ。…ま、いいよ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.easygoing.composed[1]</t>
+          <t xml:space="preserve">high_trust.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3247,14 +3247,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ元気だよ。…もう少しやらせて</t>
+          <t xml:space="preserve">…まだ必要としてくれるんだ。…じゃあもう少し</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ暴れ足りないんだよね。…もう少し付き合ってよ</t>
+          <t xml:space="preserve">…ベルト持てたしね。…十分だよ</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3311,14 +3311,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい時間だったよ。ベルトも含めてね</t>
+          <t xml:space="preserve">…ま、潮時だね。…わかったよ</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトはなかったけど、まあ…楽しかったよ</t>
+          <t xml:space="preserve">…覚悟はできてた。…最後、よろしくね</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3375,14 +3375,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、最後くらいは正直にね。…楽しかったよ</t>
+          <t xml:space="preserve">…まあ、そうだよね。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_winless.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3407,14 +3407,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…長かったね。…でもまあ、いい時間だったよ</t>
+          <t xml:space="preserve">…まあ、勝てなくなったもんね。…仕方ないか</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これからだったんだけどな。…参ったね</t>
+          <t xml:space="preserve">…まだチャンピオンだよ。…もう少し待って</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これからだったんだけどね。…仕方ないか</t>
+          <t xml:space="preserve">…邪魔なの、か。…まあ、ちょっとひどいね</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、十分やったね。…いい時間だったよ</t>
+          <t xml:space="preserve">…まだ元気だよ。…もう少しやらせて</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3535,14 +3535,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト持ったまま終わりか。…参ったね</t>
+          <t xml:space="preserve">…まだ暴れ足りないんだよね。…もう少し付き合ってよ</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">A1_champion.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3567,14 +3567,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…ここが一番しっくりくるかな</t>
+          <t xml:space="preserve">…いい時間だったよ。ベルトも含めてね</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3584,29 +3584,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっ、ありがと。まあ…のんびりやらせてもらうよ。</t>
+          <t xml:space="preserve">…ベルトはなかったけど、まあ…楽しかったよ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3616,29 +3616,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">A3_heel.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…もらえるなら、いいんじゃない。ありがとね。</t>
+          <t xml:space="preserve">…ま、最後くらいは正直にね。…楽しかったよ</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3648,29 +3648,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…ダメか。まあ…しょうがないね。</t>
+          <t xml:space="preserve">…長かったね。…でもまあ、いい時間だったよ</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3680,29 +3680,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">B1_young.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やあ社長。{tenure}まあ…お給料のことなんだけどさ。ちょっとだけ、考えてくれない？</t>
+          <t xml:space="preserve">…これからだったんだけどな。…参ったね</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3712,29 +3712,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">B2_prime.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら…まあ、そうなるかなとは思ってた。いつか上げてね。</t>
+          <t xml:space="preserve">…これからだったんだけどね。…仕方ないか</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3744,29 +3744,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">B3_older.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…社長。{tenure}ちょっと環境変えてみようかなって。…深刻な話じゃないよ。</t>
+          <t xml:space="preserve">…まあ、十分やったね。…いい時間だったよ</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3776,447 +3776,447 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ…そこまでしてくれるんだ。…じゃあ、もうちょっといようかな。</t>
+          <t xml:space="preserve">…ベルト持ったまま終わりか。…参ったね</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ…ここが一番しっくりくるかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_accept.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">おっ、ありがと。まあ…のんびりやらせてもらうよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_accept.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ…もらえるなら、いいんじゃない。ありがとね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_negotiate_refuse.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あら…ダメか。まあ…しょうがないね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_open.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やあ社長。{tenure}まあ…お給料のことなんだけどさ。ちょっとだけ、考えてくれない？</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">raise_refuse.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あらら…まあ、そうなるかなとは思ってた。いつか上げてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、代わり映えしなくてさ。新しいこと、してみたくてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ…社長。{tenure}ちょっと環境変えてみようかなって。…深刻な話じゃないよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はは。まあ、そうなるか。{tenure_farewell}{rivalry}…元気でね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ごめんね、社長。…お金の話じゃないんだ。…気持ちが、決まっちゃったから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">へえ…そこまでしてくれるんだ。…じゃあ、もうちょっといようかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing.composed[1]</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="2">
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="12">
+      <c r="D121" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.easygoing.composed[1]</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr" s="2">
+      <c r="E121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr" s="3">
+      <c r="F121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">嬉しいけど、今のメンバーが好きでね。
 …動けないんだ</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="40" customHeight="1">
-      <c r="A111" t="inlineStr" s="15">
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.easygoing.composed[1]</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr" s="2">
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="12">
+      <c r="D122" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.easygoing.composed[1]</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr" s="2">
+      <c r="E122" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr" s="3">
+      <c r="F122" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪いけど、今のとこが好きでね。
 また縁があれば</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="40" customHeight="1">
-      <c r="A112" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">スカウト？ …まあ、話は聞くよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="40" customHeight="1">
-      <c r="A113" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">新しい場所か。…悪くないね</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="40" customHeight="1">
-      <c r="A114" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あれ、なんかいい感じ。…悪くないね</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="40" customHeight="1">
-      <c r="A115" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">（…あれ、なんか今日いいね。…いつもと違う——）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="40" customHeight="1">
-      <c r="A116" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">cap_reached.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">へー、もう限界なんだ。…まあいいんじゃない？</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="40" customHeight="1">
-      <c r="A117" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_elite.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">え、もうこんなとこまで来たの？ へー</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="40" customHeight="1">
-      <c r="A118" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_growth.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あれ、なかなかいいんじゃない？</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="40" customHeight="1">
-      <c r="A119" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ovr_legend.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">へぇ〜、やるじゃん自分。…ちょっと笑っちゃうね</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="40" customHeight="1">
-      <c r="A120" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_growth.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">お、ファン増えてきた？ いいじゃんいいじゃん</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="40" customHeight="1">
-      <c r="A121" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">pop_star.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">あはは、すごいね。…嬉しいなぁ</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">…楽しいって感覚、どこ行ったかな。…困ったね</t>
-        </is>
-      </c>
-    </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4226,29 +4226,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">start.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる気、戻ってきたかな。…楽しまないとね</t>
+          <t xml:space="preserve">スカウト？ …まあ、話は聞くよ</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4258,29 +4258,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">success.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…長かったな。…まあ、また楽しくなってきた</t>
+          <t xml:space="preserve">新しい場所か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4305,14 +4305,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、おかしいな。…いつもの感覚が戻らない</t>
+          <t xml:space="preserve">あれ、なんかいい感じ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4337,14 +4337,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、治ったはずなのに。…まあ、そのうち戻るか</t>
+          <t xml:space="preserve">（…あれ、なんか今日いいね。…いつもと違う——）</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">cap_reached.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4369,14 +4369,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参ったな。…リングがちょっと遠く感じる</t>
+          <t xml:space="preserve">へー、もう限界なんだ。…まあいいんじゃない？</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.easygoing.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4401,14 +4401,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったんだけどね。…気分が乗らないなぁ</t>
+          <t xml:space="preserve">え、もうこんなとこまで来たの？ へー</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4418,29 +4418,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
+          <t xml:space="preserve">あれ、なかなかいいんじゃない？</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4450,29 +4450,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
+          <t xml:space="preserve">へぇ〜、やるじゃん自分。…ちょっと笑っちゃうね</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4482,29 +4482,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.composed[1]</t>
+          <t xml:space="preserve">pop_growth.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
+          <t xml:space="preserve">お、ファン増えてきた？ いいじゃんいいじゃん</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4514,29 +4514,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.composed[1]</t>
+          <t xml:space="preserve">pop_star.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
+          <t xml:space="preserve">あはは、すごいね。…嬉しいなぁ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4546,29 +4546,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
+          <t xml:space="preserve">…楽しいって感覚、どこ行ったかな。…困ったね</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
@@ -4588,19 +4588,19 @@
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
+          <t xml:space="preserve">…やる気、戻ってきたかな。…楽しまないとね</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4610,29 +4610,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
+          <t xml:space="preserve">…長かったな。…まあ、また楽しくなってきた</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4642,29 +4642,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">defeat.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
+          <t xml:space="preserve">…あれ、おかしいな。…いつもの感覚が戻らない</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
+          <t xml:space="preserve">…あれ、治ったはずなのに。…まあ、そのうち戻るか</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4706,29 +4706,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい日になりましたね</t>
+          <t xml:space="preserve">…参ったな。…リングがちょっと遠く感じる</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4738,29 +4738,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">penalty_end.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様に、心から感謝です</t>
+          <t xml:space="preserve">…治ったんだけどね。…気分が乗らないなぁ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4770,29 +4770,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">bestMatch.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4802,29 +4802,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">champion.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4834,29 +4834,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4866,29 +4866,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">mvp.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4898,29 +4898,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">rookie.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4930,29 +4930,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4962,29 +4962,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[3]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4994,29 +4994,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[3]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5026,29 +5026,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5058,29 +5058,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">いい日になりましたね</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[3]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5090,29 +5090,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[3]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">お客様に、心から感謝です</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5122,29 +5122,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">N1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5154,29 +5154,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">N1.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5186,29 +5186,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.composed[1]</t>
+          <t xml:space="preserve">N2.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5218,29 +5218,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">N3.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5250,29 +5250,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">N4.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5282,29 +5282,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N4.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">…もっと楽しませたいな</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5314,29 +5314,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N5_low.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5346,29 +5346,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N5_warning.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5378,29 +5378,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">faction_decree.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">E1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5442,29 +5442,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">E1.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5474,29 +5474,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">E6.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
+          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5506,29 +5506,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_boycott.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
+          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5538,29 +5538,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_boycott.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒にいると楽でいいね</t>
+          <t xml:space="preserve">…練習ね。…今日はいいや</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5570,29 +5570,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_grumble.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
+          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5602,29 +5602,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_sns.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
+          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5634,29 +5634,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">S1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
+          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5666,29 +5666,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">S1.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
+          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5698,29 +5698,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">S2.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
+          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5730,29 +5730,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">S3.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…居心地いいね。…最高だ</t>
+          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5762,29 +5762,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">S4_direct.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに、これは笑えない</t>
+          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5794,29 +5794,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">S4_silent.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
+          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5826,29 +5826,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">S5.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5858,29 +5858,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">S6.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5890,29 +5890,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.composed[2]</t>
+          <t xml:space="preserve">B1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5922,29 +5922,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5954,29 +5954,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.composed[2]</t>
+          <t xml:space="preserve">B2_fighter2.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5986,29 +5986,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_brand.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6018,29 +6018,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.composed[2]</t>
+          <t xml:space="preserve">B4_brand.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6050,29 +6050,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_cm.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6082,29 +6082,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[2]</t>
+          <t xml:space="preserve">B4_cm.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6114,29 +6114,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_fan.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6146,29 +6146,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.composed[2]</t>
+          <t xml:space="preserve">B4_fan.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6178,29 +6178,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6210,29 +6210,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.composed[2]</t>
+          <t xml:space="preserve">B4_fashion.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6274,29 +6274,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6306,29 +6306,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_variety.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6338,29 +6338,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_variety.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6370,29 +6370,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6402,29 +6402,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4.easygoing.composed[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6434,29 +6434,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
@@ -6476,19 +6476,19 @@
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
@@ -6508,19 +6508,19 @@
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
@@ -6540,19 +6540,19 @@
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
@@ -6572,19 +6572,19 @@
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6594,29 +6594,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6626,29 +6626,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6658,29 +6658,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">draftInterest.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6690,59 +6690,1915 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">draftJoin.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんかな</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一緒にいると楽でいいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…居心地いいね。…最高だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…さすがに、これは笑えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[2]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、こんなもんかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.easygoing.composed[1]</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr" s="2">
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr" s="12">
+      <c r="D257" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.easygoing.composed[1]</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr" s="2">
+      <c r="E257" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr" s="3">
+      <c r="F257" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
         </is>
       </c>
     </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H201"/>
+  <autoFilter ref="A1:H259"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -342,7 +342,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -357,7 +357,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.composed[1]</t>
+          <t xml:space="preserve">atk.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -374,7 +374,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -389,7 +389,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.composed[2]</t>
+          <t xml:space="preserve">atk.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -406,7 +406,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -421,7 +421,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.composed[3]</t>
+          <t xml:space="preserve">atk.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -438,7 +438,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.composed[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.easygoing[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -453,7 +453,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.composed[4]</t>
+          <t xml:space="preserve">atk.composed.easygoing[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -485,7 +485,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.composed[1]</t>
+          <t xml:space="preserve">bigmove.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -502,7 +502,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -517,7 +517,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.composed[2]</t>
+          <t xml:space="preserve">bigmove.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -534,7 +534,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -549,7 +549,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.composed[3]</t>
+          <t xml:space="preserve">bigmove.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -566,7 +566,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -581,7 +581,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.composed[1]</t>
+          <t xml:space="preserve">climax.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -598,7 +598,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -613,7 +613,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.composed[2]</t>
+          <t xml:space="preserve">climax.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -630,7 +630,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -645,7 +645,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">badWinner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -662,7 +662,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -677,7 +677,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">goodWinner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -694,7 +694,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -709,7 +709,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.composed[1]</t>
+          <t xml:space="preserve">competition_won.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -726,7 +726,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -741,7 +741,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.composed[1]</t>
+          <t xml:space="preserve">direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -758,7 +758,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.composed[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -773,7 +773,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.composed[1]</t>
+          <t xml:space="preserve">fa_signing.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -790,7 +790,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.composed.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -805,7 +805,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed.hit[1]</t>
+          <t xml:space="preserve">composed.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -822,7 +822,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.composed.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -837,7 +837,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed.hit[2]</t>
+          <t xml:space="preserve">composed.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -854,7 +854,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.composed.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.easygoing.win[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -869,7 +869,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed.win[1]</t>
+          <t xml:space="preserve">composed.easygoing.win[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -886,7 +886,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.composed.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.easygoing.win[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -901,7 +901,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed.win[2]</t>
+          <t xml:space="preserve">composed.easygoing.win[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -918,7 +918,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -933,7 +933,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -950,7 +950,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -965,7 +965,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -982,7 +982,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -997,7 +997,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1014,7 +1014,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1046,7 +1046,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1078,7 +1078,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1110,7 +1110,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1142,7 +1142,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1174,7 +1174,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1206,7 +1206,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1238,7 +1238,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1270,7 +1270,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1302,7 +1302,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1334,7 +1334,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1366,7 +1366,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1398,7 +1398,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1430,7 +1430,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.easygoing.composed[1]</t>
+          <t xml:space="preserve">ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1462,7 +1462,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.easygoing.composed[1]</t>
+          <t xml:space="preserve">behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1494,7 +1494,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">loser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1526,7 +1526,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">winner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1558,7 +1558,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">loser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">winner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1622,7 +1622,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1654,7 +1654,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">defender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1686,7 +1686,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1718,7 +1718,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">defender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1750,7 +1750,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1782,7 +1782,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.composed[1]</t>
+          <t xml:space="preserve">defender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1814,7 +1814,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1846,7 +1846,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateDefender.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1878,7 +1878,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1910,7 +1910,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1942,7 +1942,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateLoser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1974,7 +1974,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.easygoing.composed[1]</t>
+          <t xml:space="preserve">fateWinner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2006,7 +2006,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.composed[1]</t>
+          <t xml:space="preserve">loser.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2038,7 +2038,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.composed[1]</t>
+          <t xml:space="preserve">winner.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2070,7 +2070,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2102,7 +2102,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2134,7 +2134,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.easygoing.composed[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.easygoing.composed[1]</t>
+          <t xml:space="preserve">awakening.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2934,7 +2934,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.composed[1]</t>
+          <t xml:space="preserve">accepted.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2966,7 +2966,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.composed[2]</t>
+          <t xml:space="preserve">accepted.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2998,7 +2998,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.composed[1]</t>
+          <t xml:space="preserve">defended.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3030,7 +3030,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.composed[2]</t>
+          <t xml:space="preserve">defended.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.composed[1]</t>
+          <t xml:space="preserve">defense_failed.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3094,7 +3094,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.composed[2]</t>
+          <t xml:space="preserve">defense_failed.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3126,7 +3126,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.easygoing.composed[1]</t>
+          <t xml:space="preserve">default.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3158,7 +3158,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">former_champ.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3190,7 +3190,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3222,7 +3222,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.easygoing.composed[1]</t>
+          <t xml:space="preserve">high_trust.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3254,7 +3254,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3286,7 +3286,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3318,7 +3318,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3350,7 +3350,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3382,7 +3382,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.easygoing.composed[1]</t>
+          <t xml:space="preserve">accept_winless.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3414,7 +3414,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3446,7 +3446,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3478,7 +3478,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3542,7 +3542,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">A1_champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3606,7 +3606,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.composed[1]</t>
+          <t xml:space="preserve">A3_heel.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3638,7 +3638,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3670,7 +3670,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.composed[1]</t>
+          <t xml:space="preserve">B1_young.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3702,7 +3702,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.composed[1]</t>
+          <t xml:space="preserve">B2_prime.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3734,7 +3734,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.composed[1]</t>
+          <t xml:space="preserve">B3_older.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3766,7 +3766,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3798,7 +3798,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3830,7 +3830,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">raise_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3862,7 +3862,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3894,7 +3894,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3926,7 +3926,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">raise_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3990,7 +3990,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、代わり映えしなくてさ。新しいこと、してみたくてね。</t>
+          <t xml:space="preserve">…いやあ、ついにこの日が来たね。…じゃ、元気で。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…社長。{tenure}ちょっと環境変えてみようかなって。…深刻な話じゃないよ。</t>
+          <t xml:space="preserve">…潮時かなって。楽しかったよ、うん。…じゃあね。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4079,14 +4079,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はは。まあ、そうなるか。{tenure_farewell}{rivalry}…元気でね。</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、代わり映えしなくてさ。新しいこと、してみたくてね。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing.composed[1]</t>
+          <t xml:space="preserve">transfer_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんね、社長。…お金の話じゃないんだ。…気持ちが、決まっちゃったから。</t>
+          <t xml:space="preserve">まあ…社長。{tenure}ちょっと環境変えてみようかなって。…深刻な話じゃないよ。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.composed[1]</t>
+          <t xml:space="preserve">transfer_release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ…そこまでしてくれるんだ。…じゃあ、もうちょっといようかな。</t>
+          <t xml:space="preserve">…はは。まあ、そうなるか。{tenure_farewell}{rivalry}…元気でね。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.easygoing.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4160,127 +4160,127 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ごめんね、社長。…お金の話じゃないんだ。…気持ちが、決まっちゃったから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">へえ…そこまでしてくれるんだ。…じゃあ、もうちょっといようかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">blocked.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">blocked.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr" s="3">
+      <c r="F123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">嬉しいけど、今のメンバーが好きでね。
 …動けないんだ</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="40" customHeight="1">
-      <c r="A122" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr" s="2">
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">fail.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr" s="2">
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fail.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr" s="3">
+      <c r="F124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪いけど、今のとこが好きでね。
 また縁があれば</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="40" customHeight="1">
-      <c r="A123" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">スカウト？ …まあ、話は聞くよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">新しい場所か。…悪くないね</t>
-        </is>
-      </c>
-    </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4290,29 +4290,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">start.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、なんかいい感じ。…悪くないね</t>
+          <t xml:space="preserve">スカウト？ …まあ、話は聞くよ</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4322,29 +4322,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">success.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あれ、なんか今日いいね。…いつもと違う——）</t>
+          <t xml:space="preserve">新しい場所か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4354,29 +4354,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.easygoing.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へー、もう限界なんだ。…まあいいんじゃない？</t>
+          <t xml:space="preserve">社長、私たちのこと、たまには思い出してあげてくださいね。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4386,29 +4386,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.easygoing.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、もうこんなとこまで来たの？ へー</t>
+          <t xml:space="preserve">社長、次のメイン、私たちで請けても構いませんか。流れを作りますよ。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4418,29 +4418,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.easygoing.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、なかなかいいんじゃない？</t>
+          <t xml:space="preserve">社長、給与の話、頃合いだと思うんですけど、いかがですか?</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4450,29 +4450,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.easygoing.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ〜、やるじゃん自分。…ちょっと笑っちゃうね</t>
+          <t xml:space="preserve">社長、私たちの仕事ぶり、たまには口に出していただけると助かります。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4482,29 +4482,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、ファン増えてきた？ いいじゃんいいじゃん</t>
+          <t xml:space="preserve">ありがとうございます〜。社長にそう言ってもらえると、肩の力が抜けます。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4514,29 +4514,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、すごいね。…嬉しいなぁ</t>
+          <t xml:space="preserve">まあ、こういうこともありますね。失礼しました〜。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4546,29 +4546,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しいって感覚、どこ行ったかな。…困ったね</t>
+          <t xml:space="preserve">ふむ、別ルートですか〜。それもまた、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4578,29 +4578,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる気、戻ってきたかな。…楽しまないとね</t>
+          <t xml:space="preserve">社長、ありがとうございます。任されたからにはやりますよ。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4610,29 +4610,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…長かったな。…まあ、また楽しくなってきた</t>
+          <t xml:space="preserve">まあ、こういうこともありますね。次に期待します〜。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4642,29 +4642,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、おかしいな。…いつもの感覚が戻らない</t>
+          <t xml:space="preserve">ふむ、まあそういう手もありますね〜。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4674,29 +4674,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、治ったはずなのに。…まあ、そのうち戻るか</t>
+          <t xml:space="preserve">ありがとうございます〜。これでみんなも一息つけますね。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4706,29 +4706,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参ったな。…リングがちょっと遠く感じる</t>
+          <t xml:space="preserve">まあ、こういうご時世ですからね〜。承知しました。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4738,29 +4738,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったんだけどね。…気分が乗らないなぁ</t>
+          <t xml:space="preserve">ふむ、お金じゃないんですね〜。まあ、ありがたいですよ。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4770,29 +4770,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
+          <t xml:space="preserve">ありがとうございます〜。社長にそう言ってもらえると、嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4802,29 +4802,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
+          <t xml:space="preserve">まあ、こういうこともありますね〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4834,29 +4834,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
+          <t xml:space="preserve">ふむ、別ルートですか〜。それもまた、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4866,29 +4866,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
+          <t xml:space="preserve">あらら、気にしてましたか〜。次は誘いますね。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4898,29 +4898,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
+          <t xml:space="preserve">ありがとうございます〜。楽しんできますね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4930,29 +4930,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
+          <t xml:space="preserve">あらら、配慮足りませんでしたね〜。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4962,29 +4962,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
+          <t xml:space="preserve">ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4994,29 +4994,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
+          <t xml:space="preserve">あらら、見られてました〜? じゃ、控えますね。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5026,29 +5026,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
+          <t xml:space="preserve">ありがとうございます〜、引き続きやらせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5058,29 +5058,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい日になりましたね</t>
+          <t xml:space="preserve">あらら、見られてましたか。明日から、ちゃんとしますね。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.composed[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5090,29 +5090,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様に、心から感謝です</t>
+          <t xml:space="preserve">助かります〜、社長ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5122,29 +5122,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
+          <t xml:space="preserve">ふむ、メンバーケアですか〜。それも助かりますね。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.easygoing.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5154,29 +5154,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.easygoing.composed[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
+          <t xml:space="preserve">あらら、見ててくれたんですね〜。じゃ、休ませてもらいます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5186,29 +5186,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
+          <t xml:space="preserve">いやいや、まだ大丈夫ですよ〜。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5218,29 +5218,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
+          <t xml:space="preserve">ふむ、メンバーケアですか〜。それも助かりますね。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5250,29 +5250,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
+          <t xml:space="preserve">あらら、序列の話ですか〜。注意しておきますね。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.easygoing.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5282,29 +5282,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.easygoing.composed[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと楽しませたいな</t>
+          <t xml:space="preserve">ありがとうございます〜。穏便に〜。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5314,29 +5314,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
+          <t xml:space="preserve">ふむ、別ルートですか。下の子も助かりますね〜。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5346,29 +5346,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
+          <t xml:space="preserve">あらら、見られてましたか〜。気をつけますね。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5378,29 +5378,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
+          <t xml:space="preserve">（曖昧に微笑んで、話題を逃がした）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5410,29 +5410,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
+          <t xml:space="preserve">ふむ、別ルートで動いてくれるんですね〜。ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5442,29 +5442,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.composed[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
+          <t xml:space="preserve">あらら、見られてました? じゃ、緩めますね〜。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5474,29 +5474,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
+          <t xml:space="preserve">ありがとうございます〜。続けますね。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5506,29 +5506,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
+          <t xml:space="preserve">ふむ、私じゃなくて子たち優先ですか〜。ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.easygoing.composed[2]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.composed</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5538,29 +5538,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.easygoing.composed[2]</t>
+          <t xml:space="preserve">easygoing.attack.composed</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…練習ね。…今日はいいや</t>
+          <t xml:space="preserve">仲良しごっこは、もう終わりだ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.easygoing.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.composed</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5570,29 +5570,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.easygoing.composed[1]</t>
+          <t xml:space="preserve">easygoing.defend.composed</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">まあ、仕方ない</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.easygoing.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5602,29 +5602,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
+          <t xml:space="preserve">あれ、なんかいい感じ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5634,29 +5634,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
+          <t xml:space="preserve">（…あれ、なんか今日いいね。…いつもと違う——）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.easygoing.composed[2]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5666,29 +5666,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.easygoing.composed[2]</t>
+          <t xml:space="preserve">cap_reached.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
+          <t xml:space="preserve">へー、もう限界なんだ。…まあいいんじゃない？</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5698,29 +5698,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.easygoing.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
+          <t xml:space="preserve">え、もうこんなとこまで来たの？ へー</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5730,29 +5730,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.easygoing.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
+          <t xml:space="preserve">あれ、なかなかいいんじゃない？</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5762,29 +5762,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.easygoing.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
+          <t xml:space="preserve">へぇ〜、やるじゃん自分。…ちょっと笑っちゃうね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5794,29 +5794,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.easygoing.composed[1]</t>
+          <t xml:space="preserve">pop_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
+          <t xml:space="preserve">お、ファン増えてきた？ いいじゃんいいじゃん</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.easygoing.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5826,29 +5826,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.easygoing.composed[1]</t>
+          <t xml:space="preserve">pop_star.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
+          <t xml:space="preserve">あはは、すごいね。…嬉しいなぁ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.easygoing.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5858,29 +5858,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
+          <t xml:space="preserve">…楽しいって感覚、どこ行ったかな。…困ったね</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.easygoing.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5890,29 +5890,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
+          <t xml:space="preserve">…やる気、戻ってきたかな。…楽しまないとね</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.easygoing.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5922,29 +5922,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
+          <t xml:space="preserve">…長かったな。…まあ、また楽しくなってきた</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.easygoing.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5954,29 +5954,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.easygoing.composed[1]</t>
+          <t xml:space="preserve">defeat.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
+          <t xml:space="preserve">…あれ、おかしいな。…いつもの感覚が戻らない</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5986,29 +5986,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
+          <t xml:space="preserve">…あれ、治ったはずなのに。…まあ、そのうち戻るか</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.easygoing.composed[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6018,29 +6018,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.easygoing.composed[2]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
+          <t xml:space="preserve">…参ったな。…リングがちょっと遠く感じる</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6050,29 +6050,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing.composed[1]</t>
+          <t xml:space="preserve">penalty_end.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
+          <t xml:space="preserve">…治ったんだけどね。…気分が乗らないなぁ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.easygoing.composed[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6082,29 +6082,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.easygoing.composed[2]</t>
+          <t xml:space="preserve">bestMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
+          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6114,29 +6114,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing.composed[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
+          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.easygoing.composed[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6146,29 +6146,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.easygoing.composed[2]</t>
+          <t xml:space="preserve">hallOfFame.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
+          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6178,29 +6178,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing.composed[1]</t>
+          <t xml:space="preserve">mvp.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
+          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.easygoing.composed[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6210,29 +6210,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.easygoing.composed[2]</t>
+          <t xml:space="preserve">rookie.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
+          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
+          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.easygoing.composed[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6274,29 +6274,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
+          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6306,29 +6306,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
+          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.easygoing.composed[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6338,29 +6338,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
+          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6370,29 +6370,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
+          <t xml:space="preserve">いい日になりましたね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.easygoing.composed[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6402,29 +6402,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
+          <t xml:space="preserve">お客様に、心から感謝です</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6434,29 +6434,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6466,29 +6466,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6498,29 +6498,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6562,29 +6562,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">N4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6594,29 +6594,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.easygoing.composed[1]</t>
+          <t xml:space="preserve">N4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
+          <t xml:space="preserve">…もっと楽しませたいな</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6626,29 +6626,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.easygoing.composed[1]</t>
+          <t xml:space="preserve">N5_low.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
+          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6658,29 +6658,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.composed[1]</t>
+          <t xml:space="preserve">N5_warning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6690,29 +6690,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.composed[1]</t>
+          <t xml:space="preserve">faction_decree.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6722,29 +6722,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">E1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6754,29 +6754,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.composed[1]</t>
+          <t xml:space="preserve">E1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6786,29 +6786,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.composed[1]</t>
+          <t xml:space="preserve">E6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6818,29 +6818,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6850,29 +6850,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">…練習ね。…今日はいいや</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6882,29 +6882,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_grumble.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6914,29 +6914,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing.composed[1]</t>
+          <t xml:space="preserve">S_sns.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
+          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6946,29 +6946,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">S1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6978,29 +6978,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.composed[1]</t>
+          <t xml:space="preserve">S1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7010,29 +7010,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.composed[1]</t>
+          <t xml:space="preserve">S2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7042,29 +7042,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">S3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7074,29 +7074,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">S4_direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7106,29 +7106,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">S4_silent.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7138,29 +7138,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">S5.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7170,29 +7170,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">S6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7202,29 +7202,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">B1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7234,29 +7234,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7266,29 +7266,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
+          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7298,29 +7298,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
+          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7330,29 +7330,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒にいると楽でいいね</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7362,29 +7362,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_cm.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
+          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7394,29 +7394,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_cm.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7426,29 +7426,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
+          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7458,29 +7458,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
+          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7490,29 +7490,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
+          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7522,29 +7522,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…居心地いいね。…最高だ</t>
+          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7554,29 +7554,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに、これは笑えない</t>
+          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7586,29 +7586,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
+          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7618,29 +7618,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_variety.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7650,29 +7650,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4_variety.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7682,29 +7682,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.composed[2]</t>
+          <t xml:space="preserve">B4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7714,29 +7714,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">B4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7746,29 +7746,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7778,29 +7778,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7810,29 +7810,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7842,29 +7842,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7874,29 +7874,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7906,29 +7906,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7938,29 +7938,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.composed[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7970,29 +7970,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.composed[1]</t>
+          <t xml:space="preserve">draftInterest.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8002,29 +8002,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.composed[2]</t>
+          <t xml:space="preserve">draftJoin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8034,29 +8034,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.composed[1]</t>
+          <t xml:space="preserve">faGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8066,29 +8066,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.easygoing.composed[1]</t>
+          <t xml:space="preserve">faSigning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8098,29 +8098,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">faWelcome.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8130,29 +8130,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.easygoing.composed[1]</t>
+          <t xml:space="preserve">injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8162,29 +8162,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.composed[1]</t>
+          <t xml:space="preserve">release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8194,29 +8194,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8226,29 +8226,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.easygoing.composed[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8258,29 +8258,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8290,29 +8290,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">titleDefense.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8322,29 +8322,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">titleLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8354,29 +8354,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8386,29 +8386,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8418,29 +8418,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8450,29 +8450,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.composed[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8482,29 +8482,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんかな</t>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8514,29 +8514,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8546,29 +8546,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8578,27 +8578,1339 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一緒にいると楽でいいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…居心地いいね。…最高だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…さすがに、これは笑えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、こんなもんかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.composed[1]</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr" s="2">
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr" s="3">
+      <c r="F300" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H259"/>
+  <autoFilter ref="A1:H300"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…争奪戦だったの?…ふぅん、ありがとね</t>
+          <t xml:space="preserve">…争奪戦だったの？…ふぅん、ありがとね</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといい? ……やってみたい相手がいるの。</t>
+          <t xml:space="preserve">社長、ちょっといい？ ……やってみたい相手がいるの。</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるんだけど。……あの相手、私に回してくれない?</t>
+          <t xml:space="preserve">お願いがあるんだけど。……あの相手、私に回してくれない？</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたし? ま、いいよ。付き合う。</t>
+          <t xml:space="preserve">…私？ ま、いいよ。付き合う。</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、給与の話、頃合いだと思うんですけど、いかがですか?</t>
+          <t xml:space="preserve">社長、給与の話、頃合いだと思うんですけど、いかがですか？</t>
         </is>
       </c>
     </row>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見られてました〜? じゃ、控えますね。</t>
+          <t xml:space="preserve">あらら、見られてました〜？ じゃ、控えますね。</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見られてました? じゃ、緩めますね〜。</t>
+          <t xml:space="preserve">あらら、見られてました？ じゃ、緩めますね〜。</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しごっこは、もう終わりだ</t>
+          <t xml:space="preserve">仲良しごっこは、そろそろお開きかな〜♪</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6097,14 +6097,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
+          <t xml:space="preserve">仲間と勝つのは気持ちいいね。最高の一日だ。</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">bestMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6129,14 +6129,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
+          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6161,14 +6161,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
+          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6193,14 +6193,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
+          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.easygoing[1]</t>
+          <t xml:space="preserve">mvp.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6225,14 +6225,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
+          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">rookie.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6257,14 +6257,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
+          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">springTagChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6289,14 +6289,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
+          <t xml:space="preserve">いい相棒に恵まれたね。だから最高の結果になった。</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[3]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
+          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6353,14 +6353,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
+          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい日になりましたね</t>
+          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[3]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6417,14 +6417,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様に、心から感謝です</t>
+          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6434,29 +6434,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
+          <t xml:space="preserve">いい日になりましたね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6466,29 +6466,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
+          <t xml:space="preserve">お客様に、心から感謝です</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.easygoing[1]</t>
+          <t xml:space="preserve">N1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6513,14 +6513,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
+          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.easygoing[1]</t>
+          <t xml:space="preserve">N1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6545,14 +6545,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
+          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.easygoing[1]</t>
+          <t xml:space="preserve">N2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6577,14 +6577,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
+          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.easygoing[2]</t>
+          <t xml:space="preserve">N3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6609,14 +6609,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと楽しませたいな</t>
+          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.easygoing[1]</t>
+          <t xml:space="preserve">N4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6641,14 +6641,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
+          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.easygoing[1]</t>
+          <t xml:space="preserve">N4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6673,14 +6673,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
+          <t xml:space="preserve">…もっと楽しませたいな</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6690,29 +6690,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.easygoing[1]</t>
+          <t xml:space="preserve">N5_low.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
+          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6722,29 +6722,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
+          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.easygoing[2]</t>
+          <t xml:space="preserve">faction_decree.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6769,14 +6769,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
+          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.easygoing[1]</t>
+          <t xml:space="preserve">E1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6801,14 +6801,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
+          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.easygoing[1]</t>
+          <t xml:space="preserve">E1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6833,14 +6833,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
+          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.easygoing[2]</t>
+          <t xml:space="preserve">E6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6865,14 +6865,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…練習ね。…今日はいいや</t>
+          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6897,14 +6897,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6929,14 +6929,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
+          <t xml:space="preserve">…練習ね。…今日はいいや</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
+          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.easygoing[2]</t>
+          <t xml:space="preserve">S_sns.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6993,14 +6993,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
+          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.easygoing[1]</t>
+          <t xml:space="preserve">S1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7025,14 +7025,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
+          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.easygoing[1]</t>
+          <t xml:space="preserve">S1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7057,14 +7057,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
+          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.easygoing[1]</t>
+          <t xml:space="preserve">S2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7089,14 +7089,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
+          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.easygoing[1]</t>
+          <t xml:space="preserve">S3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7121,14 +7121,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
+          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7153,14 +7153,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
+          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.easygoing[1]</t>
+          <t xml:space="preserve">S4_silent.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7185,14 +7185,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
+          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.easygoing[1]</t>
+          <t xml:space="preserve">S5.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7217,14 +7217,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
+          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.easygoing[1]</t>
+          <t xml:space="preserve">S6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7249,14 +7249,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
+          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.easygoing[1]</t>
+          <t xml:space="preserve">B1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7281,14 +7281,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
+          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7313,14 +7313,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
+          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.easygoing[2]</t>
+          <t xml:space="preserve">B2_fighter2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7345,14 +7345,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
+          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7377,14 +7377,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
+          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_brand.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7409,14 +7409,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7441,14 +7441,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
+          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_cm.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7473,14 +7473,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7505,14 +7505,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
+          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_fan.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7537,14 +7537,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
+          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
+          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_fashion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7601,14 +7601,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
+          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7633,14 +7633,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
+          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_gravure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
+          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7697,14 +7697,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
+          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_variety.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
+          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7746,29 +7746,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7778,29 +7778,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
@@ -7825,14 +7825,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
@@ -7889,14 +7889,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7921,14 +7921,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7953,14 +7953,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7985,14 +7985,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8017,14 +8017,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8049,14 +8049,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8081,14 +8081,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8113,14 +8113,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8145,14 +8145,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8177,14 +8177,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8209,14 +8209,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8241,14 +8241,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8273,14 +8273,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8305,14 +8305,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8337,14 +8337,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8369,14 +8369,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8433,14 +8433,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
@@ -8465,14 +8465,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
@@ -8497,14 +8497,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
@@ -8529,14 +8529,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
@@ -8561,14 +8561,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8578,29 +8578,29 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8610,29 +8610,29 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8657,14 +8657,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒にいると楽でいいね</t>
+          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8689,14 +8689,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
+          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8721,14 +8721,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
+          <t xml:space="preserve">…一緒にいると楽でいいね</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8753,14 +8753,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
+          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8785,14 +8785,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
+          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8817,14 +8817,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
+          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8849,14 +8849,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…居心地いいね。…最高だ</t>
+          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8881,14 +8881,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに、これは笑えない</t>
+          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8913,14 +8913,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
+          <t xml:space="preserve">…居心地いいね。…最高だ</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8945,14 +8945,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+          <t xml:space="preserve">…さすがに、これは笑えない</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8962,29 +8962,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8994,29 +8994,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9041,14 +9041,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9073,14 +9073,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9105,14 +9105,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9137,14 +9137,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9169,14 +9169,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[2]</t>
+          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9201,14 +9201,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9233,14 +9233,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
+          <t xml:space="preserve">champion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9265,14 +9265,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
+          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9297,14 +9297,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
+          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9329,14 +9329,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9361,14 +9361,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9393,14 +9393,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9425,14 +9425,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9457,14 +9457,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+          <t xml:space="preserve">楽しかったね。…また出たいな</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9553,14 +9553,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9585,14 +9585,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+          <t xml:space="preserve">…ま、楽しんでいこうか</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">summon.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9617,14 +9617,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
@@ -9649,14 +9649,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
@@ -9681,14 +9681,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9713,14 +9713,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9745,14 +9745,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9777,14 +9777,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9809,14 +9809,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんかな</t>
+          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9826,29 +9826,29 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9858,59 +9858,123 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…ま、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr" s="2">
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr" s="12">
+      <c r="D302" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr" s="2">
+      <c r="E302" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F300" t="inlineStr" s="3">
+      <c r="F302" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H300"/>
+  <autoFilter ref="A1:H302"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3830,7 +3830,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.composed.easygoing[1]</t>
+          <t xml:space="preserve">decline_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3855,14 +3855,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おっ、ありがと。まあ…のんびりやらせてもらうよ。</t>
+          <t xml:space="preserve">はいはい、了解でーす。まあ、生活が壊れるわけじゃないしね。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.composed.easygoing[1]</t>
+          <t xml:space="preserve">decline_hold.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…もらえるなら、いいんじゃない。ありがとね。</t>
+          <t xml:space="preserve">えっ、据え置き？ …社長、あんまり優しくすると、こっちが本気出しちゃうよ？</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.composed.easygoing[1]</t>
+          <t xml:space="preserve">decline_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3919,14 +3919,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら…ダメか。まあ…しょうがないね。</t>
+          <t xml:space="preserve">あー、来たね、その話。まあ、上がる年があれば下がる年もあるよねー。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.composed.easygoing[1]</t>
+          <t xml:space="preserve">decline_strict.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3951,14 +3951,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やあ社長。{tenure}まあ…お給料のことなんだけどさ。ちょっとだけ、考えてくれない？</t>
+          <t xml:space="preserve">うわ、そこまで持っていくんだ。……あはは。…笑うしかないねー、これ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.composed.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら…まあ、そうなるかなとは思ってた。いつか上げてね。</t>
+          <t xml:space="preserve">はい、契約成立ー。……自分で言った額だし、文句のつけようがないねー。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -4015,14 +4015,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いやあ、ついにこの日が来たね。…じゃ、元気で。</t>
+          <t xml:space="preserve">あー、そう来るかー。……こっちが格好つけた分、逃げ場がなくなったんだけど？</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.easygoing[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…潮時かなって。楽しかったよ、うん。…じゃあね。</t>
+          <t xml:space="preserve">はい社長、先に言っちゃうね。ピークはとっくに置いてきたし、正直に下げていいよ〜。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.composed.easygoing[1]</t>
+          <t xml:space="preserve">raise_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4079,14 +4079,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、代わり映えしなくてさ。新しいこと、してみたくてね。</t>
+          <t xml:space="preserve">おっ、ありがと。まあ…のんびりやらせてもらうよ。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.composed.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ…社長。{tenure}ちょっと環境変えてみようかなって。…深刻な話じゃないよ。</t>
+          <t xml:space="preserve">まあ…もらえるなら、いいんじゃない。ありがとね。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.composed.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はは。まあ、そうなるか。{tenure_farewell}{rivalry}…元気でね。</t>
+          <t xml:space="preserve">あら…ダメか。まあ…しょうがないね。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.composed.easygoing[1]</t>
+          <t xml:space="preserve">raise_open.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ごめんね、社長。…お金の話じゃないんだ。…気持ちが、決まっちゃったから。</t>
+          <t xml:space="preserve">やあ社長。{tenure}まあ…お給料のことなんだけどさ。ちょっとだけ、考えてくれない？</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.composed.easygoing[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4207,304 +4207,304 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ…そこまでしてくれるんだ。…じゃあ、もうちょっといようかな。</t>
+          <t xml:space="preserve">あらら…まあ、そうなるかなとは思ってた。いつか上げてね。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いやあ、ついにこの日が来たね。…じゃ、元気で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">sudden_departure.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…潮時かなって。楽しかったよ、うん。…じゃあね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_listen.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…まあ、代わり映えしなくてさ。新しいこと、してみたくてね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_open.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ…社長。{tenure}ちょっと環境変えてみようかなって。…深刻な話じゃないよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_release.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…はは。まあ、そうなるか。{tenure_farewell}{rivalry}…元気でね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_fail.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ごめんね、社長。…お金の話じゃないんだ。…気持ちが、決まっちゃったから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">transfer_retain_success.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">06 契約交渉</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">へえ…そこまでしてくれるんだ。…じゃあ、もうちょっといようかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr" s="2">
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="D130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">blocked.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr" s="2">
+      <c r="E130" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr" s="3">
+      <c r="F130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">嬉しいけど、今のメンバーが好きでね。
 …動けないんだ</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="40" customHeight="1">
-      <c r="A124" t="inlineStr" s="15">
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr" s="2">
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="D131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fail.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr" s="2">
+      <c r="E131" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr" s="3">
+      <c r="F131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">悪いけど、今のとこが好きでね。
 また縁があれば</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="40" customHeight="1">
-      <c r="A125" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">start.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">スカウト？ …まあ、話は聞くよ</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="40" customHeight="1">
-      <c r="A126" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">success.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">06 契約交渉</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">新しい場所か。…悪くないね</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="40" customHeight="1">
-      <c r="A127" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちのこと、たまには思い出してあげてくださいね。</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="40" customHeight="1">
-      <c r="A128" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、次のメイン、私たちで請けても構いませんか。流れを作りますよ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="40" customHeight="1">
-      <c r="A129" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、給与の話、頃合いだと思うんですけど、いかがですか？</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="40" customHeight="1">
-      <c r="A130" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">社長、私たちの仕事ぶり、たまには口に出していただけると助かります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="40" customHeight="1">
-      <c r="A131" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">F07_LINES</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.easygoing[1]</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">ありがとうございます〜。社長にそう言ってもらえると、肩の力が抜けます。</t>
-        </is>
-      </c>
-    </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4514,29 +4514,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">start.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こういうこともありますね。失礼しました〜。</t>
+          <t xml:space="preserve">スカウト？ …まあ、話は聞くよ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4546,29 +4546,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">success.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、別ルートですか〜。それもまた、ありがたいです。</t>
+          <t xml:space="preserve">新しい場所か。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ありがとうございます。任されたからにはやりますよ。</t>
+          <t xml:space="preserve">社長、私たちのこと、たまには思い出してあげてくださいね。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こういうこともありますね。次に期待します〜。</t>
+          <t xml:space="preserve">社長、次のメイン、私たちで請けても構いませんか。流れを作りますよ。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4657,14 +4657,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、まあそういう手もありますね〜。ありがとうございます。</t>
+          <t xml:space="preserve">社長、給与の話、頃合いだと思うんですけど、いかがですか？</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4689,14 +4689,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。これでみんなも一息つけますね。</t>
+          <t xml:space="preserve">社長、私たちの仕事ぶり、たまには口に出していただけると助かります。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4721,14 +4721,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こういうご時世ですからね〜。承知しました。</t>
+          <t xml:space="preserve">ありがとうございます〜。社長にそう言ってもらえると、肩の力が抜けます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、お金じゃないんですね〜。まあ、ありがたいですよ。</t>
+          <t xml:space="preserve">まあ、こういうこともありますね。失礼しました〜。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4785,14 +4785,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。社長にそう言ってもらえると、嬉しいです。</t>
+          <t xml:space="preserve">ふむ、別ルートですか〜。それもまた、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4817,14 +4817,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、こういうこともありますね〜。</t>
+          <t xml:space="preserve">社長、ありがとうございます。任されたからにはやりますよ。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4849,14 +4849,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、別ルートですか〜。それもまた、ありがたいです。</t>
+          <t xml:space="preserve">まあ、こういうこともありますね。次に期待します〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4881,14 +4881,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、気にしてましたか〜。次は誘いますね。</t>
+          <t xml:space="preserve">ふむ、まあそういう手もありますね〜。ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4913,14 +4913,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。楽しんできますね。</t>
+          <t xml:space="preserve">ありがとうございます〜。これでみんなも一息つけますね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、配慮足りませんでしたね〜。気をつけます。</t>
+          <t xml:space="preserve">まあ、こういうご時世ですからね〜。承知しました。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4977,14 +4977,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。</t>
+          <t xml:space="preserve">ふむ、お金じゃないんですね〜。まあ、ありがたいですよ。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5009,14 +5009,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見られてました〜？ じゃ、控えますね。</t>
+          <t xml:space="preserve">ありがとうございます〜。社長にそう言ってもらえると、嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5041,14 +5041,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜、引き続きやらせていただきます。</t>
+          <t xml:space="preserve">まあ、こういうこともありますね〜。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見られてましたか。明日から、ちゃんとしますね。</t>
+          <t xml:space="preserve">ふむ、別ルートですか〜。それもまた、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5105,14 +5105,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">助かります〜、社長ありがとうございます。</t>
+          <t xml:space="preserve">あらら、気にしてましたか〜。次は誘いますね。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5137,14 +5137,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、メンバーケアですか〜。それも助かりますね。</t>
+          <t xml:space="preserve">ありがとうございます〜。楽しんできますね。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見ててくれたんですね〜。じゃ、休ませてもらいます。</t>
+          <t xml:space="preserve">あらら、配慮足りませんでしたね〜。気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5201,14 +5201,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやいや、まだ大丈夫ですよ〜。</t>
+          <t xml:space="preserve">ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5233,14 +5233,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、メンバーケアですか〜。それも助かりますね。</t>
+          <t xml:space="preserve">あらら、見られてました〜？ じゃ、控えますね。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、序列の話ですか〜。注意しておきますね。</t>
+          <t xml:space="preserve">ありがとうございます〜、引き続きやらせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。穏便に〜。</t>
+          <t xml:space="preserve">あらら、見られてましたか。明日から、ちゃんとしますね。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、別ルートですか。下の子も助かりますね〜。</t>
+          <t xml:space="preserve">助かります〜、社長ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見られてましたか〜。気をつけますね。</t>
+          <t xml:space="preserve">ふむ、メンバーケアですか〜。それも助かりますね。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（曖昧に微笑んで、話題を逃がした）</t>
+          <t xml:space="preserve">あらら、見ててくれたんですね〜。じゃ、休ませてもらいます。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5425,14 +5425,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、別ルートで動いてくれるんですね〜。ありがたいです。</t>
+          <t xml:space="preserve">いやいや、まだ大丈夫ですよ〜。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5457,14 +5457,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あらら、見られてました？ じゃ、緩めますね〜。</t>
+          <t xml:space="preserve">ふむ、メンバーケアですか〜。それも助かりますね。</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5489,14 +5489,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。続けますね。</t>
+          <t xml:space="preserve">あらら、序列の話ですか〜。注意しておきますね。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5521,14 +5521,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふむ、私じゃなくて子たち優先ですか〜。ありがたいです。</t>
+          <t xml:space="preserve">ありがとうございます〜。穏便に〜。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5553,14 +5553,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しごっこは、そろそろお開きかな〜♪</t>
+          <t xml:space="preserve">ふむ、別ルートですか。下の子も助かりますね〜。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5585,14 +5585,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、仕方ない</t>
+          <t xml:space="preserve">あらら、見られてましたか〜。気をつけますね。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5602,29 +5602,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、なんかいい感じ。…悪くないね</t>
+          <t xml:space="preserve">（曖昧に微笑んで、話題を逃がした）</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5634,29 +5634,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…あれ、なんか今日いいね。…いつもと違う——）</t>
+          <t xml:space="preserve">ふむ、別ルートで動いてくれるんですね〜。ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5666,29 +5666,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へー、もう限界なんだ。…まあいいんじゃない？</t>
+          <t xml:space="preserve">あらら、見られてました？ じゃ、緩めますね〜。</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5698,29 +5698,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、もうこんなとこまで来たの？ へー</t>
+          <t xml:space="preserve">ありがとうございます〜。続けますね。</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5730,29 +5730,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.composed.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、なかなかいいんじゃない？</t>
+          <t xml:space="preserve">ふむ、私じゃなくて子たち優先ですか〜。ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.composed</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5762,29 +5762,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.composed.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.attack.composed</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へぇ〜、やるじゃん自分。…ちょっと笑っちゃうね</t>
+          <t xml:space="preserve">仲良しごっこは、そろそろお開きかな〜♪</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.composed</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5794,29 +5794,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.composed.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.defend.composed</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、ファン増えてきた？ いいじゃんいいじゃん</t>
+          <t xml:space="preserve">まあ、仕方ない</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.easygoing[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5841,14 +5841,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、すごいね。…嬉しいなぁ</t>
+          <t xml:space="preserve">あれ、なんかいい感じ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
@@ -5873,14 +5873,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しいって感覚、どこ行ったかな。…困ったね</t>
+          <t xml:space="preserve">（…あれ、なんか今日いいね。…いつもと違う——）</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">cap_reached.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5905,14 +5905,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やる気、戻ってきたかな。…楽しまないとね</t>
+          <t xml:space="preserve">へー、もう限界なんだ。…まあいいんじゃない？</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5937,14 +5937,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…長かったな。…まあ、また楽しくなってきた</t>
+          <t xml:space="preserve">え、もうこんなとこまで来たの？ へー</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.composed.easygoing[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5969,14 +5969,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、おかしいな。…いつもの感覚が戻らない</t>
+          <t xml:space="preserve">あれ、なかなかいいんじゃない？</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.composed.easygoing[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -6001,14 +6001,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、治ったはずなのに。…まあ、そのうち戻るか</t>
+          <t xml:space="preserve">へぇ〜、やるじゃん自分。…ちょっと笑っちゃうね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.composed.easygoing[1]</t>
+          <t xml:space="preserve">pop_growth.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6033,14 +6033,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…参ったな。…リングがちょっと遠く感じる</t>
+          <t xml:space="preserve">お、ファン増えてきた？ いいじゃんいいじゃん</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.easygoing[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.composed.easygoing[1]</t>
+          <t xml:space="preserve">pop_star.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6065,14 +6065,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…治ったんだけどね。…気分が乗らないなぁ</t>
+          <t xml:space="preserve">あはは、すごいね。…嬉しいなぁ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6082,29 +6082,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間と勝つのは気持ちいいね。最高の一日だ。</t>
+          <t xml:space="preserve">…楽しいって感覚、どこ行ったかな。…困ったね</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6114,29 +6114,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
+          <t xml:space="preserve">…やる気、戻ってきたかな。…楽しまないとね</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6146,29 +6146,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
+          <t xml:space="preserve">…長かったな。…まあ、また楽しくなってきた</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6178,29 +6178,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.easygoing[1]</t>
+          <t xml:space="preserve">defeat.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
+          <t xml:space="preserve">…あれ、おかしいな。…いつもの感覚が戻らない</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6210,29 +6210,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.easygoing[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
+          <t xml:space="preserve">…あれ、治ったはずなのに。…まあ、そのうち戻るか</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6242,29 +6242,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.easygoing[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
+          <t xml:space="preserve">…参ったな。…リングがちょっと遠く感じる</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6274,29 +6274,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.composed.easygoing[1]</t>
+          <t xml:space="preserve">penalty_end.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい相棒に恵まれたね。だから最高の結果になった。</t>
+          <t xml:space="preserve">…治ったんだけどね。…気分が乗らないなぁ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
+          <t xml:space="preserve">仲間と勝つのは気持ちいいね。最高の一日だ。</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">bestMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6353,14 +6353,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
+          <t xml:space="preserve">あの試合は楽しかったな。…全部出し切れた</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[3]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6385,14 +6385,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
+          <t xml:space="preserve">チャンピオンか。…まあ、楽しんでいくよ</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6417,14 +6417,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
+          <t xml:space="preserve">楽しかったな。…全部ひっくるめて、いい時間だった</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">mvp.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6449,14 +6449,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい日になりましたね</t>
+          <t xml:space="preserve">MVP？ …ふぅん。悪くないね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[3]</t>
+          <t xml:space="preserve">rookie.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様に、心から感謝です</t>
+          <t xml:space="preserve">へえ、新人王か。…悪くないね。来年も楽しみだ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6498,29 +6498,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.easygoing[1]</t>
+          <t xml:space="preserve">springTagChampion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
+          <t xml:space="preserve">いい相棒に恵まれたね。だから最高の結果になった。</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6530,29 +6530,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
+          <t xml:space="preserve">ドーム、いいじゃないですか。いきましょう</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6562,29 +6562,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
+          <t xml:space="preserve">あまり肩に力を入れずに、でも全力で</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6594,29 +6594,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
+          <t xml:space="preserve">こういう日こそ、いつも通りが大事ですね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6626,29 +6626,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
+          <t xml:space="preserve">満員。嬉しいですね、素直に</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6658,29 +6658,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと楽しませたいな</t>
+          <t xml:space="preserve">いい日になりましたね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.easygoing[3]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6690,29 +6690,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[3]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
+          <t xml:space="preserve">お客様に、心から感謝です</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.easygoing[1]</t>
+          <t xml:space="preserve">N1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6737,14 +6737,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
+          <t xml:space="preserve">…なんか今日、急に掴めた気がするね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6754,29 +6754,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.easygoing[1]</t>
+          <t xml:space="preserve">N1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
+          <t xml:space="preserve">…よくわからないけど、噛み合ってきたよ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6786,29 +6786,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.easygoing[1]</t>
+          <t xml:space="preserve">N2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
+          <t xml:space="preserve">…あの人といると楽しいね。最高の相棒だよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6818,29 +6818,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.easygoing[2]</t>
+          <t xml:space="preserve">N3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
+          <t xml:space="preserve">…ちょっと疲れたかな。…少し休めば平気だよ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6850,29 +6850,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.easygoing[1]</t>
+          <t xml:space="preserve">N4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
+          <t xml:space="preserve">…ファンが喜んでくれるのが一番だね</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6882,29 +6882,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.easygoing[1]</t>
+          <t xml:space="preserve">N4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
+          <t xml:space="preserve">…もっと楽しませたいな</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6914,29 +6914,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.easygoing[2]</t>
+          <t xml:space="preserve">N5_low.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…練習ね。…今日はいいや</t>
+          <t xml:space="preserve">…もう、いいかなって。…少し考えさせて</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.easygoing[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6946,29 +6946,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.easygoing[1]</t>
+          <t xml:space="preserve">N5_warning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
+          <t xml:space="preserve">…いや、ちょっとね。…大丈夫、大丈夫</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.easygoing[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.easygoing[1]</t>
+          <t xml:space="preserve">faction_decree.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6993,14 +6993,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
+          <t xml:space="preserve">ま、そういうこともあるさ。またどこかで</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.easygoing[1]</t>
+          <t xml:space="preserve">E1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7025,14 +7025,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
+          <t xml:space="preserve">…もっと近くで見てもらいたくてさ。出してよ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.easygoing[2]</t>
+          <t xml:space="preserve">E1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7057,14 +7057,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
+          <t xml:space="preserve">…テレビか。いいね、出るよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.easygoing[1]</t>
+          <t xml:space="preserve">E6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7089,14 +7089,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
+          <t xml:space="preserve">…他所が私を欲しいってさ。…ちょっと嬉しいかもね</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7121,14 +7121,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
+          <t xml:space="preserve">…今日は、休ませてもらおうかな</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_boycott.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7153,14 +7153,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
+          <t xml:space="preserve">…練習ね。…今日はいいや</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_grumble.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7185,14 +7185,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
+          <t xml:space="preserve">（いつもの飄々とした顔が消え、「…ちょっとさ」と珍しく愚痴をこぼしている）</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.easygoing[1]</t>
+          <t xml:space="preserve">S_sns.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7217,14 +7217,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
+          <t xml:space="preserve">（SNSに「…最近、少し考えることがあってね」と珍しく本音めいた投稿）</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.easygoing[1]</t>
+          <t xml:space="preserve">S1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7249,14 +7249,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
+          <t xml:space="preserve">…ねえ、タイトル戦って組めないかな</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.easygoing[1]</t>
+          <t xml:space="preserve">S1.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7281,14 +7281,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
+          <t xml:space="preserve">…ベルト、ちょっと欲しくなってさ。挑ませてよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7298,12 +7298,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.easygoing[1]</t>
+          <t xml:space="preserve">S2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7313,14 +7313,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
+          <t xml:space="preserve">…ねえ、あの人との試合、組んでくれない？ 決着つけたくてさ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.easygoing[1]</t>
+          <t xml:space="preserve">S3.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7345,14 +7345,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
+          <t xml:space="preserve">…ま、限界みたいでさ。ちょっと休ませてよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.easygoing[1]</t>
+          <t xml:space="preserve">S4_direct.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7377,14 +7377,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
+          <t xml:space="preserve">…正直、不満があってさ。…一度、ちゃんと話そうよ</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.easygoing[2]</t>
+          <t xml:space="preserve">S4_silent.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7409,14 +7409,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
+          <t xml:space="preserve">…いや、なんでもないよ（笑ってみせたが、目は笑っていない）</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.easygoing[1]</t>
+          <t xml:space="preserve">S5.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7441,14 +7441,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
+          <t xml:space="preserve">…特訓させてよ。もっと強くなりたくてさ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.easygoing[2]</t>
+          <t xml:space="preserve">S6.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7473,14 +7473,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
+          <t xml:space="preserve">…後輩の面倒、見させてよ。…案外、向いてる気がしてさ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.easygoing[1]</t>
+          <t xml:space="preserve">B1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7505,14 +7505,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
+          <t xml:space="preserve">…いてて。やっちゃったものは仕方ないね。ちゃんと治すよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.easygoing[2]</t>
+          <t xml:space="preserve">B2_fighter1.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7537,14 +7537,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
+          <t xml:space="preserve">…あの人とはもう無理かな。顔も合わせたくないよ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.easygoing[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7569,14 +7569,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
+          <t xml:space="preserve">…売られたなら、買うよ。…いつでもどうぞ</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_brand.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7601,14 +7601,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
+          <t xml:space="preserve">…コラボか。…商品ってもらえたりするのかな</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_brand.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7633,14 +7633,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_cm.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7665,14 +7665,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
+          <t xml:space="preserve">…CMか。…売れっ子になったのかな</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_cm.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7697,14 +7697,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
+          <t xml:space="preserve">…どんなのになるんだろうね。ちょっと楽しみ</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_fan.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
+          <t xml:space="preserve">…みんなに会えるんだ。…気分が上がるね</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_fan.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7761,14 +7761,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
+          <t xml:space="preserve">…笑顔が見られるかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.easygoing[2]</t>
+          <t xml:space="preserve">B4_fashion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7793,14 +7793,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
+          <t xml:space="preserve">…ファッションショーか。キラキラしてそうだね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7810,29 +7810,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
+          <t xml:space="preserve">…衣装、かわいいのかな。…楽しみだよ</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7842,29 +7842,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
+          <t xml:space="preserve">…グラビアか。どんな感じになるんだろうね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7874,29 +7874,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">…かわいく撮ってもらえるかな。…期待しておくよ</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7906,29 +7906,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">…バラエティか。笑わせにいこうかな</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7938,29 +7938,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">B4_variety.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">…テレビは楽しそうだね。全力でやるよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7970,29 +7970,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
+          <t xml:space="preserve">…テレビに出られるんだ。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.easygoing[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8002,29 +8002,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.easygoing[1]</t>
+          <t xml:space="preserve">B4.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
+          <t xml:space="preserve">…ファンにもう少し近づける。…いい話だよ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8056,7 +8056,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8088,7 +8088,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8113,14 +8113,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8145,14 +8145,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…新天地か。…楽しみだね</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8177,14 +8177,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8209,14 +8209,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
+          <t xml:space="preserve">…また同じ顔か。…終わったって言ったんだけどな</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.easygoing[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8241,14 +8241,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
+          <t xml:space="preserve">…忘れたふりが下手でさ。…まだ引きずってるよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8273,14 +8273,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
+          <t xml:space="preserve">…楽しくやろう。退屈にはさせないよ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8305,14 +8305,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
+          <t xml:space="preserve">…よろしく。楽しくやろうね</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8337,14 +8337,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8369,14 +8369,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…新天地か。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…よろしくね。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">injury.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8433,14 +8433,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…ま、すぐ戻るよ。心配しないで</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">release.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8472,7 +8472,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8504,7 +8504,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8529,14 +8529,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
+          <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8561,14 +8561,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8593,14 +8593,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8625,14 +8625,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8642,29 +8642,29 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8674,29 +8674,29 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
+          <t xml:space="preserve">…ま、縁がなかったってことだね。元気で</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8706,29 +8706,29 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一緒にいると楽でいいね</t>
+          <t xml:space="preserve">…おじゃまします。楽しくやろう</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8738,29 +8738,29 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8770,29 +8770,29 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
+          <t xml:space="preserve">…防衛。…まあ、こんなもんかな</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8802,29 +8802,29 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
+          <t xml:space="preserve">…ベルトがない景色か。…まあ、立ち上がるよ</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8834,29 +8834,29 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
+          <t xml:space="preserve">…チャンピオンだ。…いい気分だね</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8881,14 +8881,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
+          <t xml:space="preserve">…合わないなぁ。…まあ、そういうこともある</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8913,14 +8913,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…居心地いいね。…最高だ</t>
+          <t xml:space="preserve">…あれ、なんか距離感変わった？</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8945,14 +8945,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに、これは笑えない</t>
+          <t xml:space="preserve">…一緒にいると楽でいいね</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8977,14 +8977,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
+          <t xml:space="preserve">…最高の相棒だよ。ずっとこの距離がいいね</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9009,14 +9009,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+          <t xml:space="preserve">…一段落かぁ。…まあ、そういうもんだね</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9026,29 +9026,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+          <t xml:space="preserve">…いい相手だね。…負けたくないな</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9058,29 +9058,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+          <t xml:space="preserve">…本気でやれる相手。…楽しみだね</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9090,29 +9090,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+          <t xml:space="preserve">…ずっとやり合っていたいね。…最高の相手だ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9122,29 +9122,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+          <t xml:space="preserve">…居心地いいね。…最高だ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9154,29 +9154,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+          <t xml:space="preserve">…さすがに、これは笑えない</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9186,29 +9186,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.composed[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+          <t xml:space="preserve">…最近ちょっとモヤモヤするなぁ</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9218,29 +9218,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9265,14 +9265,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9297,14 +9297,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9329,14 +9329,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9361,14 +9361,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
+          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9393,14 +9393,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9425,14 +9425,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9457,14 +9457,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9553,14 +9553,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9585,14 +9585,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9617,14 +9617,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9649,14 +9649,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9681,14 +9681,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9713,14 +9713,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9745,14 +9745,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+          <t xml:space="preserve">楽しかったね。…また出たいな</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9777,14 +9777,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9809,14 +9809,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+          <t xml:space="preserve">…ま、楽しんでいこうか</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">summon.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9841,14 +9841,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9873,14 +9873,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんかな</t>
+          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
@@ -9932,49 +9932,273 @@
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、こんなもんかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr" s="2">
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr" s="12">
+      <c r="D309" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr" s="2">
+      <c r="E309" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr" s="3">
+      <c r="F309" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H302"/>
+  <autoFilter ref="A1:H309"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
@@ -284,7 +284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8984,7 +8984,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9009,14 +9009,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
+          <t xml:space="preserve">…いい試合だったなぁ。…負けたけどね</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9026,29 +9026,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
+          <t xml:space="preserve">…最高だね。…こういう試合のためにやってる</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9058,29 +9058,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
+          <t xml:space="preserve">GL-01.loss.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
+          <t xml:space="preserve">…負けちゃったか。…まあ次があるよ</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9090,29 +9090,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">GL-01.win.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
+          <t xml:space="preserve">…勝った〜。…いい感じだね</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9122,29 +9122,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
+          <t xml:space="preserve">GL-02.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
+          <t xml:space="preserve">…いい汗だね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9154,29 +9154,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
+          <t xml:space="preserve">GL-03.down.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
+          <t xml:space="preserve">…う〜ん、ちょっと気になるなぁ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9186,29 +9186,29 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
+          <t xml:space="preserve">GL-03.up.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
+          <t xml:space="preserve">…いい感じだね。居心地いいや</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9218,29 +9218,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
+          <t xml:space="preserve">…好調タイム終了か。…まあ楽しかった</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9265,14 +9265,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
+          <t xml:space="preserve">…さすがに疲れたね。でも、最後の一戦だ。…ま、立つよ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9297,14 +9297,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
+          <t xml:space="preserve">ここまで来たか。…傷だらけだけど、悪くない気分だよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9329,14 +9329,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
+          <t xml:space="preserve">…相手が来るね。ま、真っ向から受けるよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9361,14 +9361,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
+          <t xml:space="preserve">一戦ずつか。…慌てない慌てない。ちゃんと繋ぐから</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
+          <t xml:space="preserve">survivor.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9393,14 +9393,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
+          <t xml:space="preserve">…一人、片づけたよ。息は上がってるけど、まだ立てる。次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9410,12 +9410,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.easygoing[1]</t>
+          <t xml:space="preserve">survivor.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9425,14 +9425,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
+          <t xml:space="preserve">ふぅ…一人か。…このリング、まだ渡さないよ。次は誰かな</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9457,14 +9457,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">いい三人だった。誰が欠けても……この結果にはならなかったよ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
+          <t xml:space="preserve">最高のチームだった。こういう勝ちは、格別だね</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
+          <t xml:space="preserve">defiant.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9521,14 +9521,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しかったね。…また出たいな</t>
+          <t xml:space="preserve">個人の評価は……まあ、ありがたいけどね。次は全員で勝ちたいよ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
+          <t xml:space="preserve">defiant.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9553,14 +9553,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
+          <t xml:space="preserve">一人で目立っても仕方ない。次は、三人揃って笑おう</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9585,14 +9585,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、楽しんでいこうか</t>
+          <t xml:space="preserve">何人来ても……まあ、楽しかったかな。身体は悲鳴を上げてるけど</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.composed.easygoing[2]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9617,14 +9617,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
+          <t xml:space="preserve">次から次へと。退屈しない一日だった。さすがに疲れたけどね</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">champion.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9649,14 +9649,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
+          <t xml:space="preserve">優勝しちゃったね。…ふぅん、悪くない</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">postLose.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9681,14 +9681,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9713,14 +9713,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
+          <t xml:space="preserve">勝ったね。…この調子で行こうか</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9730,12 +9730,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">postWin.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9745,14 +9745,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+          <t xml:space="preserve">楽しかったね。…また出たいな</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9777,14 +9777,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+          <t xml:space="preserve">決勝か。…ま、ここまで来たらやるだけだね</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9809,14 +9809,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+          <t xml:space="preserve">…ま、楽しんでいこうか</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[1]</t>
+          <t xml:space="preserve">summon.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9841,14 +9841,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+          <t xml:space="preserve">…ふぅん。いい舞台だね</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.easygoing[2]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9873,14 +9873,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ま、こんなもんかな</t>
+          <t xml:space="preserve">いい舞台だね。…楽しもうか</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9890,29 +9890,29 @@
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+          <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+          <t xml:space="preserve">勝っちゃった。…ふぅん。…悪くないね</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.easygoing[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D301" t="inlineStr" s="12">
@@ -9932,49 +9932,273 @@
       </c>
       <c r="E301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+          <t xml:space="preserve">…面白そうだね。付き合ってよ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…逃げるんだ。…つまんないね</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けたか。…ま、次があるさ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…楽しかったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ったね。…うちの団体、なかなかでしょ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ま、こんなもんかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="40" customHeight="1">
+      <c r="A307" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…いい景色だね。…みんなのおかげだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" ht="40" customHeight="1">
+      <c r="A308" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…フリーはここまでにするよ。落ち着くとこだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="40" customHeight="1">
+      <c r="A309" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr" s="2">
+      <c r="B309" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr" s="12">
+      <c r="D309" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.easygoing[1]</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr" s="2">
+      <c r="E309" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr" s="3">
+      <c r="F309" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">…見つけてくれたんだ。じゃ、応えようか</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H302"/>
+  <autoFilter ref="A1:H309"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×お気楽.xlsx
@@ -2287,7 +2287,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、ちょっといい？ ……やってみたい相手がいるの。</t>
+          <t xml:space="preserve">社長、ちょっといい？ ……三人で行ってみたい所があるの。</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あのね。あの人と、やらせてもらえないかな。</t>
+          <t xml:space="preserve">……あのね。三人であちらへ、行かせてもらえないかな。</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お願いがあるんだけど。……あの相手、私に回してくれない？</t>
+          <t xml:space="preserve">お願いがあるんだけど。……あの団体、私たち三人に回してくれない？</t>
         </is>
       </c>
     </row>
